--- a/resources/templates/standard/A6200-04.xlsx
+++ b/resources/templates/standard/A6200-04.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>분임조 활동 결과 보고서</t>
   </si>
@@ -754,7 +757,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -762,7 +767,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -789,17 +794,17 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH1" s="3"/>
       <c r="AI1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
@@ -939,7 +944,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -962,7 +967,7 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
@@ -987,7 +992,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1033,7 +1038,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -1048,7 +1053,7 @@
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
       <c r="N7" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="13"/>
@@ -1653,7 +1658,7 @@
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -1875,7 +1880,7 @@
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -2097,7 +2102,7 @@
     </row>
     <row r="31" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
